--- a/event_feedback_forms/011_workshop_participant_expectation_check_in_form--event_feedback_forms.xlsx
+++ b/event_feedback_forms/011_workshop_participant_expectation_check_in_form--event_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>participant_expectation</t>
+          <t>participant_expectation_rate</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Participant Expectation</t>
+          <t>Participant Expectation Rate</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>readiness</t>
+          <t>readiness_rate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Readiness</t>
+          <t>Readiness Rate</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>session_topics</t>
+          <t>session_topics_interested</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Session Topics</t>
+          <t>Session Topics Interested</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,16 +727,62 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>follow_up_questions</t>
+          <t>follow_up_questions_ask</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Follow Up Questions</t>
+          <t>Follow Up Questions Asked</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>participant_notes_comments</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Participant Notes/Comments</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>participant_engagement</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Participant Engagement</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -753,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -803,63 +849,63 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>session_topics_choices</t>
+          <t>topics_interests_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>session_topics_choices</t>
+          <t>topics_interests_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>session_topics_choices</t>
+          <t>topics_interests_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
@@ -871,12 +917,63 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>session_topics_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>session_topics_interested_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>session_topics_interested_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
